--- a/data/MSFT/MSFT_Financial_Analysis.xlsx
+++ b/data/MSFT/MSFT_Financial_Analysis.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sentiment Analysis" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Price" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Price" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sentiment Analysis" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,9 +28,9 @@
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="+0.00%;-0.00%;0.00%"/>
     <numFmt numFmtId="168" formatCode="+$#,##0.00;-$#,##0.00;&quot;$0.00&quot;"/>
-    <numFmt numFmtId="169" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="170" formatCode="0.0&quot; d&quot;"/>
-    <numFmt numFmtId="171" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.0&quot; d&quot;"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -302,22 +302,22 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -339,7 +339,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -420,7 +435,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
   <chart>
     <title>
       <tx>
@@ -1007,362 +1021,370 @@
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="21" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B4" s="38" t="n"/>
+        <v>2016</v>
+      </c>
+      <c r="B4" s="54" t="n">
+        <v>51.16999816894531</v>
+      </c>
       <c r="C4" s="24" t="n"/>
-      <c r="D4" s="23" t="n"/>
+      <c r="D4" s="23" t="n">
+        <v>0.5226</v>
+      </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F4" s="38" t="n">
-        <v>200</v>
-      </c>
-      <c r="G4" s="38" t="n">
-        <v>38</v>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+      <c r="F4" s="54" t="n">
+        <v>85.31999999999999</v>
+      </c>
+      <c r="G4" s="54" t="n">
+        <v>16.798</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>0.235</v>
+        <v>0.236544772620722</v>
       </c>
       <c r="I4" s="39" t="n">
-        <v>0.4222222222222222</v>
-      </c>
-      <c r="J4" s="40" t="n">
-        <v>1.052631578947368</v>
-      </c>
-      <c r="K4" s="40" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.2333152770254316</v>
+      </c>
+      <c r="J4" s="55" t="n">
+        <v>2.338697523318318</v>
+      </c>
+      <c r="K4" s="55" t="n">
+        <v>0.9088712029667902</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="26" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B5" s="41" t="n">
-        <v>51.16999816894531</v>
-      </c>
-      <c r="C5" s="29" t="n"/>
-      <c r="D5" s="28" t="n"/>
+        <v>2017</v>
+      </c>
+      <c r="B5" s="56" t="n">
+        <v>68.93000030517578</v>
+      </c>
+      <c r="C5" s="44" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>0.526</v>
+      </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F5" s="41" t="n">
-        <v>216</v>
-      </c>
-      <c r="G5" s="41" t="n">
-        <v>41.8</v>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+      <c r="F5" s="56" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="G5" s="56" t="n">
+        <v>21.204</v>
       </c>
       <c r="H5" s="42" t="n">
-        <v>0.2415277777777778</v>
+        <v>0.2482045580878266</v>
       </c>
       <c r="I5" s="42" t="n">
-        <v>0.4300411522633745</v>
-      </c>
-      <c r="J5" s="43" t="n">
-        <v>1.06265664160401</v>
-      </c>
-      <c r="K5" s="43" t="n">
-        <v>0.8919753086419753</v>
+        <v>0.2467044410057127</v>
+      </c>
+      <c r="J5" s="57" t="n">
+        <v>2.359981693093572</v>
+      </c>
+      <c r="K5" s="57" t="n">
+        <v>1.033729304587604</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="21" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B6" s="38" t="n">
-        <v>68.93000030517578</v>
+        <v>2018</v>
+      </c>
+      <c r="B6" s="54" t="n">
+        <v>98.61000061035156</v>
       </c>
       <c r="C6" s="44" t="n">
-        <v>0.3471</v>
+        <v>0.4305999999999999</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>0.526</v>
+        <v>0.7429</v>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
           <t>Cautious / Negative</t>
         </is>
       </c>
-      <c r="F6" s="38" t="n">
-        <v>233.28</v>
-      </c>
-      <c r="G6" s="38" t="n">
-        <v>45.98</v>
+      <c r="F6" s="54" t="n">
+        <v>110.36</v>
+      </c>
+      <c r="G6" s="54" t="n">
+        <v>16.571</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>0.2482368827160494</v>
+        <v>0.3176694454512505</v>
       </c>
       <c r="I6" s="39" t="n">
-        <v>0.4380048773052888</v>
-      </c>
-      <c r="J6" s="40" t="n">
-        <v>1.072777181047858</v>
-      </c>
-      <c r="K6" s="40" t="n">
-        <v>0.8424211248285323</v>
+        <v>0.2003312459198723</v>
+      </c>
+      <c r="J6" s="55" t="n">
+        <v>2.242124319467202</v>
+      </c>
+      <c r="K6" s="55" t="n">
+        <v>0.9698735462656254</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="26" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B7" s="41" t="n">
-        <v>98.61000061035156</v>
+        <v>2019</v>
+      </c>
+      <c r="B7" s="56" t="n">
+        <v>133.9600067138672</v>
       </c>
       <c r="C7" s="44" t="n">
-        <v>0.4305999999999999</v>
+        <v>0.3585</v>
       </c>
       <c r="D7" s="28" t="n">
-        <v>0.7429</v>
-      </c>
-      <c r="E7" s="26" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-      <c r="F7" s="41" t="n">
-        <v>251.9424</v>
-      </c>
-      <c r="G7" s="41" t="n">
-        <v>50.578</v>
+        <v>1.0692</v>
+      </c>
+      <c r="E7" s="45" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F7" s="56" t="n">
+        <v>125.843</v>
+      </c>
+      <c r="G7" s="56" t="n">
+        <v>39.24</v>
       </c>
       <c r="H7" s="42" t="n">
-        <v>0.2551323516803841</v>
+        <v>0.3413698020549415</v>
       </c>
       <c r="I7" s="42" t="n">
-        <v>0.4461160787368683</v>
-      </c>
-      <c r="J7" s="43" t="n">
-        <v>1.082994106581647</v>
-      </c>
-      <c r="K7" s="43" t="n">
-        <v>0.7956199512269471</v>
+        <v>0.3834652594547054</v>
+      </c>
+      <c r="J7" s="57" t="n">
+        <v>2.817668207498716</v>
+      </c>
+      <c r="K7" s="57" t="n">
+        <v>0.7579106811296785</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="21" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B8" s="38" t="n">
-        <v>133.9600067138672</v>
+        <v>2020</v>
+      </c>
+      <c r="B8" s="54" t="n">
+        <v>203.5099945068359</v>
       </c>
       <c r="C8" s="44" t="n">
-        <v>0.3585</v>
+        <v>0.5192</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>1.0692</v>
+        <v>1.25</v>
       </c>
       <c r="E8" s="45" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F8" s="38" t="n">
-        <v>272.097792</v>
-      </c>
-      <c r="G8" s="38" t="n">
-        <v>55.6358</v>
+      <c r="F8" s="54" t="n">
+        <v>143.015</v>
+      </c>
+      <c r="G8" s="54" t="n">
+        <v>44.281</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>0.2622193614492836</v>
+        <v>0.3703038142852149</v>
       </c>
       <c r="I8" s="39" t="n">
-        <v>0.4543774876023658</v>
-      </c>
-      <c r="J8" s="40" t="n">
-        <v>1.093308336168139</v>
-      </c>
-      <c r="K8" s="40" t="n">
-        <v>0.75141884282545</v>
+        <v>0.374298417635921</v>
+      </c>
+      <c r="J8" s="55" t="n">
+        <v>2.517854671280277</v>
+      </c>
+      <c r="K8" s="55" t="n">
+        <v>0.6229628753043008</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="26" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B9" s="41" t="n">
-        <v>203.5099945068359</v>
+        <v>2021</v>
+      </c>
+      <c r="B9" s="56" t="n">
+        <v>270.8999938964844</v>
       </c>
       <c r="C9" s="44" t="n">
-        <v>0.5192</v>
+        <v>0.3311</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>1.25</v>
+        <v>1.2661</v>
       </c>
       <c r="E9" s="45" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F9" s="41" t="n">
-        <v>293.86561536</v>
-      </c>
-      <c r="G9" s="41" t="n">
-        <v>61.19938</v>
+      <c r="F9" s="56" t="n">
+        <v>168.088</v>
+      </c>
+      <c r="G9" s="56" t="n">
+        <v>61.271</v>
       </c>
       <c r="H9" s="42" t="n">
-        <v>0.2695032326006526</v>
+        <v>0.415948788729713</v>
       </c>
       <c r="I9" s="42" t="n">
-        <v>0.4627918855209281</v>
-      </c>
-      <c r="J9" s="43" t="n">
-        <v>1.103720796512597</v>
-      </c>
-      <c r="K9" s="43" t="n">
-        <v>0.7096733515573694</v>
+        <v>0.4315223821731414</v>
+      </c>
+      <c r="J9" s="57" t="n">
+        <v>2.418087909494907</v>
+      </c>
+      <c r="K9" s="57" t="n">
+        <v>0.3953643969912951</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="21" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B10" s="38" t="n">
-        <v>270.8999938964844</v>
-      </c>
-      <c r="C10" s="44" t="n">
-        <v>0.3311</v>
+        <v>2022</v>
+      </c>
+      <c r="B10" s="54" t="n">
+        <v>256.8299865722656</v>
+      </c>
+      <c r="C10" s="46" t="n">
+        <v>-0.0519</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>1.2661</v>
+        <v>1.5481</v>
       </c>
       <c r="E10" s="45" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F10" s="38" t="n">
-        <v>317.3748645888</v>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>67.319318</v>
+      <c r="F10" s="54" t="n">
+        <v>198.27</v>
+      </c>
+      <c r="G10" s="54" t="n">
+        <v>72.738</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>0.2769894335062358</v>
+        <v>0.4205527815604983</v>
       </c>
       <c r="I10" s="39" t="n">
-        <v>0.4713621056231676</v>
-      </c>
-      <c r="J10" s="40" t="n">
-        <v>1.114232423146007</v>
-      </c>
-      <c r="K10" s="40" t="n">
-        <v>0.6702470542486269</v>
+        <v>0.4367546925099975</v>
+      </c>
+      <c r="J10" s="55" t="n">
+        <v>1.811899202793378</v>
+      </c>
+      <c r="K10" s="55" t="n">
+        <v>0.3866712300800999</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="26" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B11" s="41" t="n">
-        <v>256.8299865722656</v>
-      </c>
-      <c r="C11" s="46" t="n">
-        <v>-0.0519</v>
+        <v>2023</v>
+      </c>
+      <c r="B11" s="56" t="n">
+        <v>340.5400085449219</v>
+      </c>
+      <c r="C11" s="44" t="n">
+        <v>0.3259</v>
       </c>
       <c r="D11" s="28" t="n">
-        <v>1.5481</v>
-      </c>
-      <c r="E11" s="45" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="F11" s="41" t="n">
-        <v>342.7648537559</v>
-      </c>
-      <c r="G11" s="41" t="n">
-        <v>74.05124979999999</v>
+        <v>0.9308</v>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+      <c r="F11" s="56" t="n">
+        <v>211.915</v>
+      </c>
+      <c r="G11" s="56" t="n">
+        <v>72.361</v>
       </c>
       <c r="H11" s="42" t="n">
-        <v>0.28468358443696</v>
+        <v>0.417728806361041</v>
       </c>
       <c r="I11" s="42" t="n">
-        <v>0.4800910335050681</v>
-      </c>
-      <c r="J11" s="43" t="n">
-        <v>1.124844160509408</v>
-      </c>
-      <c r="K11" s="43" t="n">
-        <v>0.6330111067903643</v>
+        <v>0.3508871464385641</v>
+      </c>
+      <c r="J11" s="57" t="n">
+        <v>1.76916725076573</v>
+      </c>
+      <c r="K11" s="57" t="n">
+        <v>0.3068425927272904</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="21" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B12" s="38" t="n">
-        <v>340.5400085449219</v>
+        <v>2024</v>
+      </c>
+      <c r="B12" s="54" t="n">
+        <v>446.9500122070312</v>
       </c>
       <c r="C12" s="44" t="n">
-        <v>0.3259</v>
+        <v>0.3125</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>0.9308</v>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-      <c r="F12" s="38" t="n">
-        <v>370.18604205638</v>
-      </c>
-      <c r="G12" s="38" t="n">
-        <v>81.45637478</v>
+        <v>1.0635</v>
+      </c>
+      <c r="E12" s="45" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F12" s="54" t="n">
+        <v>245.122</v>
+      </c>
+      <c r="G12" s="54" t="n">
+        <v>88.136</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>0.2925914617824345</v>
+        <v>0.4464429957327372</v>
       </c>
       <c r="I12" s="39" t="n">
-        <v>0.4889816081996146</v>
-      </c>
-      <c r="J12" s="40" t="n">
-        <v>1.135556962037985</v>
-      </c>
-      <c r="K12" s="40" t="n">
-        <v>0.5978438230797758</v>
+        <v>0.3282813797829982</v>
+      </c>
+      <c r="J12" s="55" t="n">
+        <v>1.274954903181521</v>
+      </c>
+      <c r="K12" s="55" t="n">
+        <v>0.2648346040815414</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="26" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B13" s="41" t="n">
-        <v>446.9500122070312</v>
+        <v>2025</v>
+      </c>
+      <c r="B13" s="56" t="n">
+        <v>497.4100036621094</v>
       </c>
       <c r="C13" s="44" t="n">
-        <v>0.3125</v>
+        <v>0.1129</v>
       </c>
       <c r="D13" s="28" t="n">
-        <v>1.0635</v>
+        <v>1.1466</v>
       </c>
       <c r="E13" s="45" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F13" s="41" t="n">
-        <v>399.80092542089</v>
-      </c>
-      <c r="G13" s="41" t="n">
-        <v>89.602012258</v>
+      <c r="F13" s="56" t="n">
+        <v>281.724</v>
+      </c>
+      <c r="G13" s="56" t="n">
+        <v>101.832</v>
       </c>
       <c r="H13" s="42" t="n">
-        <v>0.3007190023875017</v>
+        <v>0.4562195624085985</v>
       </c>
       <c r="I13" s="42" t="n">
-        <v>0.4980368231662731</v>
-      </c>
-      <c r="J13" s="43" t="n">
-        <v>1.14637179024789</v>
-      </c>
-      <c r="K13" s="43" t="n">
-        <v>0.5646302773531547</v>
+        <v>0.2964722734140952</v>
+      </c>
+      <c r="J13" s="57" t="n">
+        <v>1.353446444504242</v>
+      </c>
+      <c r="K13" s="57" t="n">
+        <v>0.2042948768338093</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1414,7 @@
       </c>
       <c r="B18" s="49" t="inlineStr">
         <is>
-          <t>$446.95</t>
+          <t>$497.41</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1426,7 @@
       </c>
       <c r="B19" s="49" t="inlineStr">
         <is>
-          <t>+773.46%</t>
+          <t>+872.07%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1438,7 @@
       </c>
       <c r="B20" s="49" t="inlineStr">
         <is>
-          <t>+31.12%</t>
+          <t>+28.75%</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1450,7 @@
       </c>
       <c r="B21" s="49" t="inlineStr">
         <is>
-          <t>1.05x</t>
+          <t>1.01x</t>
         </is>
       </c>
     </row>
@@ -1499,34 +1521,34 @@
         </is>
       </c>
       <c r="C3" s="37" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D3" s="37" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E3" s="37" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="F3" s="37" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G3" s="37" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H3" s="37" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="37" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="37" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="37" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="37" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1558,35 +1580,35 @@
           <t>Total Current Assets / Total Current Liabilities</t>
         </is>
       </c>
-      <c r="C5" s="43" t="n">
-        <v>1.052631578947368</v>
-      </c>
-      <c r="D5" s="43" t="n">
-        <v>1.06265664160401</v>
-      </c>
-      <c r="E5" s="43" t="n">
-        <v>1.072777181047858</v>
-      </c>
-      <c r="F5" s="43" t="n">
-        <v>1.082994106581647</v>
-      </c>
-      <c r="G5" s="43" t="n">
-        <v>1.093308336168139</v>
-      </c>
-      <c r="H5" s="43" t="n">
-        <v>1.103720796512597</v>
-      </c>
-      <c r="I5" s="43" t="n">
-        <v>1.114232423146007</v>
-      </c>
-      <c r="J5" s="43" t="n">
-        <v>1.124844160509408</v>
-      </c>
-      <c r="K5" s="43" t="n">
-        <v>1.135556962037985</v>
-      </c>
-      <c r="L5" s="43" t="n">
-        <v>1.14637179024789</v>
+      <c r="C5" s="57" t="n">
+        <v>2.338697523318318</v>
+      </c>
+      <c r="D5" s="57" t="n">
+        <v>2.359981693093572</v>
+      </c>
+      <c r="E5" s="57" t="n">
+        <v>2.242124319467202</v>
+      </c>
+      <c r="F5" s="57" t="n">
+        <v>2.817668207498716</v>
+      </c>
+      <c r="G5" s="57" t="n">
+        <v>2.517854671280277</v>
+      </c>
+      <c r="H5" s="57" t="n">
+        <v>2.418087909494907</v>
+      </c>
+      <c r="I5" s="57" t="n">
+        <v>1.811899202793378</v>
+      </c>
+      <c r="J5" s="57" t="n">
+        <v>1.76916725076573</v>
+      </c>
+      <c r="K5" s="57" t="n">
+        <v>1.274954903181521</v>
+      </c>
+      <c r="L5" s="57" t="n">
+        <v>1.353446444504242</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1600,35 +1622,35 @@
           <t>(Cash + Mkt Securities + Accounts Rec) / Current Liab</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n">
-        <v>0.8105263157894737</v>
-      </c>
-      <c r="D6" s="40" t="n">
-        <v>0.8097243107769424</v>
-      </c>
-      <c r="E6" s="40" t="n">
-        <v>0.8089719536937582</v>
-      </c>
-      <c r="F6" s="40" t="n">
-        <v>0.8082691717957025</v>
-      </c>
-      <c r="G6" s="40" t="n">
-        <v>0.8076158968417697</v>
-      </c>
-      <c r="H6" s="40" t="n">
-        <v>0.8070120650875702</v>
-      </c>
-      <c r="I6" s="40" t="n">
-        <v>0.8064576172791317</v>
-      </c>
-      <c r="J6" s="40" t="n">
-        <v>0.8059524986472458</v>
-      </c>
-      <c r="K6" s="40" t="n">
-        <v>0.805496658901629</v>
-      </c>
-      <c r="L6" s="40" t="n">
-        <v>0.8050900522265916</v>
+      <c r="C6" s="55" t="n">
+        <v>2.202337692784299</v>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>2.255484690111318</v>
+      </c>
+      <c r="E6" s="55" t="n">
+        <v>2.117566996141445</v>
+      </c>
+      <c r="F6" s="55" t="n">
+        <v>2.621709681561376</v>
+      </c>
+      <c r="G6" s="55" t="n">
+        <v>2.332705882352941</v>
+      </c>
+      <c r="H6" s="55" t="n">
+        <v>2.207267674318</v>
+      </c>
+      <c r="I6" s="55" t="n">
+        <v>1.567173597526346</v>
+      </c>
+      <c r="J6" s="55" t="n">
+        <v>1.535780468367435</v>
+      </c>
+      <c r="K6" s="55" t="n">
+        <v>1.06485960123238</v>
+      </c>
+      <c r="L6" s="55" t="n">
+        <v>1.164653231174496</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1642,35 +1664,35 @@
           <t>(Cash &amp; Cash Equiv + Mkt Securities) / Current Liab</t>
         </is>
       </c>
-      <c r="C7" s="43" t="n">
-        <v>0.5789473684210527</v>
-      </c>
-      <c r="D7" s="43" t="n">
-        <v>0.5759398496240602</v>
-      </c>
-      <c r="E7" s="43" t="n">
-        <v>0.5729609738632295</v>
-      </c>
-      <c r="F7" s="43" t="n">
-        <v>0.5700104683477401</v>
-      </c>
-      <c r="G7" s="43" t="n">
-        <v>0.5670880628847792</v>
-      </c>
-      <c r="H7" s="43" t="n">
-        <v>0.5641934898547988</v>
-      </c>
-      <c r="I7" s="43" t="n">
-        <v>0.5613264841870259</v>
-      </c>
-      <c r="J7" s="43" t="n">
-        <v>0.5584867833351821</v>
-      </c>
-      <c r="K7" s="43" t="n">
-        <v>0.5556741272532553</v>
-      </c>
-      <c r="L7" s="43" t="n">
-        <v>0.5528882583720518</v>
+      <c r="C7" s="57" t="n">
+        <v>1.896277441934457</v>
+      </c>
+      <c r="D7" s="57" t="n">
+        <v>1.963282841704314</v>
+      </c>
+      <c r="E7" s="57" t="n">
+        <v>1.767640995824304</v>
+      </c>
+      <c r="F7" s="57" t="n">
+        <v>2.147839625064201</v>
+      </c>
+      <c r="G7" s="57" t="n">
+        <v>1.889647058823529</v>
+      </c>
+      <c r="H7" s="57" t="n">
+        <v>1.708558918763027</v>
+      </c>
+      <c r="I7" s="57" t="n">
+        <v>1.101670137355125</v>
+      </c>
+      <c r="J7" s="57" t="n">
+        <v>1.068296383066568</v>
+      </c>
+      <c r="K7" s="57" t="n">
+        <v>0.6029723991507431</v>
+      </c>
+      <c r="L7" s="57" t="n">
+        <v>0.6696384313614412</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1684,35 +1706,35 @@
           <t>Cash Flow from Operations / Current Liabilities</t>
         </is>
       </c>
-      <c r="C8" s="40" t="n">
-        <v>0.7368421052631579</v>
-      </c>
-      <c r="D8" s="40" t="n">
-        <v>0.7649122807017544</v>
-      </c>
-      <c r="E8" s="40" t="n">
-        <v>0.7940517961570593</v>
-      </c>
-      <c r="F8" s="40" t="n">
-        <v>0.8243013883916139</v>
-      </c>
-      <c r="G8" s="40" t="n">
-        <v>0.8557033460446278</v>
-      </c>
-      <c r="H8" s="40" t="n">
-        <v>0.8883015687510898</v>
-      </c>
-      <c r="I8" s="40" t="n">
-        <v>0.9221416285129999</v>
-      </c>
-      <c r="J8" s="40" t="n">
-        <v>0.9572708334088104</v>
-      </c>
-      <c r="K8" s="40" t="n">
-        <v>0.9937382937290871</v>
-      </c>
-      <c r="L8" s="40" t="n">
-        <v>1.031594990633053</v>
+      <c r="C8" s="55" t="n">
+        <v>0.5580487968250247</v>
+      </c>
+      <c r="D8" s="55" t="n">
+        <v>0.5832668969793604</v>
+      </c>
+      <c r="E8" s="55" t="n">
+        <v>0.5798932290290184</v>
+      </c>
+      <c r="F8" s="55" t="n">
+        <v>0.8375866718027735</v>
+      </c>
+      <c r="G8" s="55" t="n">
+        <v>0.8397923875432526</v>
+      </c>
+      <c r="H8" s="55" t="n">
+        <v>1.005990849861699</v>
+      </c>
+      <c r="I8" s="55" t="n">
+        <v>0.9364022633095643</v>
+      </c>
+      <c r="J8" s="55" t="n">
+        <v>0.84092982169776</v>
+      </c>
+      <c r="K8" s="55" t="n">
+        <v>0.9462190508117427</v>
+      </c>
+      <c r="L8" s="55" t="n">
+        <v>0.9641971986573949</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1744,35 +1766,35 @@
           <t>Total Debt (Short + Long-Term) / Stockholders' Equity</t>
         </is>
       </c>
-      <c r="C10" s="40" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="D10" s="40" t="n">
-        <v>0.8919753086419753</v>
-      </c>
-      <c r="E10" s="40" t="n">
-        <v>0.8424211248285323</v>
-      </c>
-      <c r="F10" s="40" t="n">
-        <v>0.7956199512269471</v>
-      </c>
-      <c r="G10" s="40" t="n">
-        <v>0.75141884282545</v>
-      </c>
-      <c r="H10" s="40" t="n">
-        <v>0.7096733515573694</v>
-      </c>
-      <c r="I10" s="40" t="n">
-        <v>0.6702470542486269</v>
-      </c>
-      <c r="J10" s="40" t="n">
-        <v>0.6330111067903643</v>
-      </c>
-      <c r="K10" s="40" t="n">
-        <v>0.5978438230797758</v>
-      </c>
-      <c r="L10" s="40" t="n">
-        <v>0.5646302773531547</v>
+      <c r="C10" s="55" t="n">
+        <v>0.9088712029667902</v>
+      </c>
+      <c r="D10" s="55" t="n">
+        <v>1.033729304587604</v>
+      </c>
+      <c r="E10" s="55" t="n">
+        <v>0.9698735462656254</v>
+      </c>
+      <c r="F10" s="55" t="n">
+        <v>0.7579106811296785</v>
+      </c>
+      <c r="G10" s="55" t="n">
+        <v>0.6229628753043008</v>
+      </c>
+      <c r="H10" s="55" t="n">
+        <v>0.3953643969912951</v>
+      </c>
+      <c r="I10" s="55" t="n">
+        <v>0.3866712300800999</v>
+      </c>
+      <c r="J10" s="55" t="n">
+        <v>0.3068425927272904</v>
+      </c>
+      <c r="K10" s="55" t="n">
+        <v>0.2648346040815414</v>
+      </c>
+      <c r="L10" s="55" t="n">
+        <v>0.2042948768338093</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1786,35 +1808,35 @@
           <t>Total Debt / Total Assets</t>
         </is>
       </c>
-      <c r="C11" s="43" t="n">
-        <v>0.2428571428571429</v>
-      </c>
-      <c r="D11" s="43" t="n">
-        <v>0.2336927223719676</v>
-      </c>
-      <c r="E11" s="43" t="n">
-        <v>0.2248741290749123</v>
-      </c>
-      <c r="F11" s="43" t="n">
-        <v>0.2163883128834062</v>
-      </c>
-      <c r="G11" s="43" t="n">
-        <v>0.2082227161708248</v>
-      </c>
-      <c r="H11" s="43" t="n">
-        <v>0.2003652551832465</v>
-      </c>
-      <c r="I11" s="43" t="n">
-        <v>0.1928043021574636</v>
-      </c>
-      <c r="J11" s="43" t="n">
-        <v>0.1855286681137866</v>
-      </c>
-      <c r="K11" s="43" t="n">
-        <v>0.178527586298168</v>
-      </c>
-      <c r="L11" s="43" t="n">
-        <v>0.1717906962491903</v>
+      <c r="C11" s="57" t="n">
+        <v>0.3378318378473262</v>
+      </c>
+      <c r="D11" s="57" t="n">
+        <v>0.3685323909310371</v>
+      </c>
+      <c r="E11" s="57" t="n">
+        <v>0.3099347879836816</v>
+      </c>
+      <c r="F11" s="57" t="n">
+        <v>0.2706521587403509</v>
+      </c>
+      <c r="G11" s="57" t="n">
+        <v>0.2445944555625251</v>
+      </c>
+      <c r="H11" s="57" t="n">
+        <v>0.1681861351373214</v>
+      </c>
+      <c r="I11" s="57" t="n">
+        <v>0.1765075101414319</v>
+      </c>
+      <c r="J11" s="57" t="n">
+        <v>0.1535963259995728</v>
+      </c>
+      <c r="K11" s="57" t="n">
+        <v>0.1388268969058679</v>
+      </c>
+      <c r="L11" s="57" t="n">
+        <v>0.1133613245816256</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1828,35 +1850,35 @@
           <t>Total Assets / Total Stockholders' Equity</t>
         </is>
       </c>
-      <c r="C12" s="40" t="n">
-        <v>3.888888888888889</v>
-      </c>
-      <c r="D12" s="40" t="n">
-        <v>3.816872427983539</v>
-      </c>
-      <c r="E12" s="40" t="n">
-        <v>3.746189605243103</v>
-      </c>
-      <c r="F12" s="40" t="n">
-        <v>3.676815723664527</v>
-      </c>
-      <c r="G12" s="40" t="n">
-        <v>3.608726543596666</v>
-      </c>
-      <c r="H12" s="40" t="n">
-        <v>3.541898274270801</v>
-      </c>
-      <c r="I12" s="40" t="n">
-        <v>3.476307565488009</v>
-      </c>
-      <c r="J12" s="40" t="n">
-        <v>3.411931499460408</v>
-      </c>
-      <c r="K12" s="40" t="n">
-        <v>3.348747582803738</v>
-      </c>
-      <c r="L12" s="40" t="n">
-        <v>3.286733738677749</v>
+      <c r="C12" s="55" t="n">
+        <v>2.690306540550301</v>
+      </c>
+      <c r="D12" s="55" t="n">
+        <v>2.80498900510768</v>
+      </c>
+      <c r="E12" s="55" t="n">
+        <v>3.129282622887401</v>
+      </c>
+      <c r="F12" s="55" t="n">
+        <v>2.800312713769178</v>
+      </c>
+      <c r="G12" s="55" t="n">
+        <v>2.54692149039762</v>
+      </c>
+      <c r="H12" s="55" t="n">
+        <v>2.350754993379722</v>
+      </c>
+      <c r="I12" s="55" t="n">
+        <v>2.190678627613455</v>
+      </c>
+      <c r="J12" s="55" t="n">
+        <v>1.997720913768105</v>
+      </c>
+      <c r="K12" s="55" t="n">
+        <v>1.907660618972947</v>
+      </c>
+      <c r="L12" s="55" t="n">
+        <v>1.802156754852553</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1870,55 +1892,35 @@
           <t>Operating Income (EBIT) / Interest Expense</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C13" s="57" t="n">
+        <v>16.23652453740949</v>
+      </c>
+      <c r="D13" s="57" t="n">
+        <v>14.24760689215061</v>
+      </c>
+      <c r="E13" s="57" t="n">
+        <v>15.69292748433304</v>
+      </c>
+      <c r="F13" s="57" t="n">
+        <v>15.49747474747475</v>
+      </c>
+      <c r="G13" s="57" t="n">
+        <v>20.43959861057507</v>
+      </c>
+      <c r="H13" s="57" t="n">
+        <v>29.80221653878943</v>
+      </c>
+      <c r="I13" s="57" t="n">
+        <v>40.41832283082889</v>
+      </c>
+      <c r="J13" s="57" t="n">
+        <v>44.98119918699187</v>
+      </c>
+      <c r="K13" s="57" t="n">
+        <v>37.28551959114139</v>
+      </c>
+      <c r="L13" s="57" t="n">
+        <v>45.90285714285714</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1950,35 +1952,35 @@
           <t>Total Revenues / Total Assets</t>
         </is>
       </c>
-      <c r="C15" s="43" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="D15" s="43" t="n">
-        <v>0.5822102425876011</v>
-      </c>
-      <c r="E15" s="43" t="n">
-        <v>0.5931953415043483</v>
-      </c>
-      <c r="F15" s="43" t="n">
-        <v>0.6043877064383926</v>
-      </c>
-      <c r="G15" s="43" t="n">
-        <v>0.6157912480693056</v>
-      </c>
-      <c r="H15" s="43" t="n">
-        <v>0.6274099508630662</v>
-      </c>
-      <c r="I15" s="43" t="n">
-        <v>0.639247874464256</v>
-      </c>
-      <c r="J15" s="43" t="n">
-        <v>0.6513091551145126</v>
-      </c>
-      <c r="K15" s="43" t="n">
-        <v>0.6635980070978299</v>
-      </c>
-      <c r="L15" s="43" t="n">
-        <v>0.6761187242128798</v>
+      <c r="C15" s="57" t="n">
+        <v>0.440488605738949</v>
+      </c>
+      <c r="D15" s="57" t="n">
+        <v>0.3731033738997702</v>
+      </c>
+      <c r="E15" s="57" t="n">
+        <v>0.4263505995796761</v>
+      </c>
+      <c r="F15" s="57" t="n">
+        <v>0.439156744231494</v>
+      </c>
+      <c r="G15" s="57" t="n">
+        <v>0.4746424790332912</v>
+      </c>
+      <c r="H15" s="57" t="n">
+        <v>0.5035906992351227</v>
+      </c>
+      <c r="I15" s="57" t="n">
+        <v>0.5434437013485364</v>
+      </c>
+      <c r="J15" s="57" t="n">
+        <v>0.5143867603938094</v>
+      </c>
+      <c r="K15" s="57" t="n">
+        <v>0.4786015389631816</v>
+      </c>
+      <c r="L15" s="57" t="n">
+        <v>0.4551254194244616</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1992,35 +1994,35 @@
           <t>Total Revenues / Accounts Receivable, Net</t>
         </is>
       </c>
-      <c r="C16" s="40" t="n">
-        <v>9.090909090909092</v>
-      </c>
-      <c r="D16" s="40" t="n">
-        <v>9.262435677530018</v>
-      </c>
-      <c r="E16" s="40" t="n">
-        <v>9.437198614841904</v>
-      </c>
-      <c r="F16" s="40" t="n">
-        <v>9.615258966065337</v>
-      </c>
-      <c r="G16" s="40" t="n">
-        <v>9.796678946557135</v>
-      </c>
-      <c r="H16" s="40" t="n">
-        <v>9.98152194554878</v>
-      </c>
-      <c r="I16" s="40" t="n">
-        <v>10.16985254829563</v>
-      </c>
-      <c r="J16" s="40" t="n">
-        <v>10.36173655864003</v>
-      </c>
-      <c r="K16" s="40" t="n">
-        <v>10.5572410220104</v>
-      </c>
-      <c r="L16" s="40" t="n">
-        <v>10.75643424884101</v>
+      <c r="C16" s="55" t="n">
+        <v>4.668162171034633</v>
+      </c>
+      <c r="D16" s="55" t="n">
+        <v>4.544765561843169</v>
+      </c>
+      <c r="E16" s="55" t="n">
+        <v>4.167516332464786</v>
+      </c>
+      <c r="F16" s="55" t="n">
+        <v>4.262396694214876</v>
+      </c>
+      <c r="G16" s="55" t="n">
+        <v>4.467682983974258</v>
+      </c>
+      <c r="H16" s="55" t="n">
+        <v>4.418368688063507</v>
+      </c>
+      <c r="I16" s="55" t="n">
+        <v>4.479564402069542</v>
+      </c>
+      <c r="J16" s="55" t="n">
+        <v>4.352509858692081</v>
+      </c>
+      <c r="K16" s="55" t="n">
+        <v>4.235881661712864</v>
+      </c>
+      <c r="L16" s="55" t="n">
+        <v>4.030097990129462</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -2034,35 +2036,35 @@
           <t>(Accounts Receivable * 365) / Total Revenues</t>
         </is>
       </c>
-      <c r="C17" s="53" t="n">
-        <v>40.15</v>
-      </c>
-      <c r="D17" s="53" t="n">
-        <v>39.40648148148148</v>
-      </c>
-      <c r="E17" s="53" t="n">
-        <v>38.67673182441701</v>
-      </c>
-      <c r="F17" s="53" t="n">
-        <v>37.96049604989076</v>
-      </c>
-      <c r="G17" s="53" t="n">
-        <v>37.25752390081872</v>
-      </c>
-      <c r="H17" s="53" t="n">
-        <v>36.56756975450726</v>
-      </c>
-      <c r="I17" s="53" t="n">
-        <v>35.89039253682891</v>
-      </c>
-      <c r="J17" s="53" t="n">
-        <v>35.22575563800149</v>
-      </c>
-      <c r="K17" s="53" t="n">
-        <v>34.57342682989098</v>
-      </c>
-      <c r="L17" s="53" t="n">
-        <v>33.9331781848923</v>
+      <c r="C17" s="58" t="n">
+        <v>78.18922878574779</v>
+      </c>
+      <c r="D17" s="58" t="n">
+        <v>80.31217342968316</v>
+      </c>
+      <c r="E17" s="58" t="n">
+        <v>87.58214026821311</v>
+      </c>
+      <c r="F17" s="58" t="n">
+        <v>85.63257392147359</v>
+      </c>
+      <c r="G17" s="58" t="n">
+        <v>81.69782889906654</v>
+      </c>
+      <c r="H17" s="58" t="n">
+        <v>82.6096746942078</v>
+      </c>
+      <c r="I17" s="58" t="n">
+        <v>81.48113683361073</v>
+      </c>
+      <c r="J17" s="58" t="n">
+        <v>83.85966071302173</v>
+      </c>
+      <c r="K17" s="58" t="n">
+        <v>86.16860175749218</v>
+      </c>
+      <c r="L17" s="58" t="n">
+        <v>90.56851741420681</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -2076,35 +2078,35 @@
           <t>Cost of Goods Sold / Inventories</t>
         </is>
       </c>
-      <c r="C18" s="40" t="n">
-        <v>30</v>
-      </c>
-      <c r="D18" s="40" t="n">
-        <v>31.16504854368932</v>
-      </c>
-      <c r="E18" s="40" t="n">
-        <v>32.37534169101706</v>
-      </c>
-      <c r="F18" s="40" t="n">
-        <v>33.63263651396918</v>
-      </c>
-      <c r="G18" s="40" t="n">
-        <v>34.93875832033692</v>
-      </c>
-      <c r="H18" s="40" t="n">
-        <v>36.29560330365097</v>
-      </c>
-      <c r="I18" s="40" t="n">
-        <v>37.70514129599419</v>
-      </c>
-      <c r="J18" s="40" t="n">
-        <v>39.1694186279058</v>
-      </c>
-      <c r="K18" s="40" t="n">
-        <v>40.69056109890071</v>
-      </c>
-      <c r="L18" s="40" t="n">
-        <v>42.27077706387859</v>
+      <c r="C18" s="55" t="n">
+        <v>14.56241670368725</v>
+      </c>
+      <c r="D18" s="55" t="n">
+        <v>15.70884915176524</v>
+      </c>
+      <c r="E18" s="55" t="n">
+        <v>14.40758827948911</v>
+      </c>
+      <c r="F18" s="55" t="n">
+        <v>20.79980610761028</v>
+      </c>
+      <c r="G18" s="55" t="n">
+        <v>24.3155672823219</v>
+      </c>
+      <c r="H18" s="55" t="n">
+        <v>19.81487101669196</v>
+      </c>
+      <c r="I18" s="55" t="n">
+        <v>16.74238375200428</v>
+      </c>
+      <c r="J18" s="55" t="n">
+        <v>26.3452</v>
+      </c>
+      <c r="K18" s="55" t="n">
+        <v>24.43587207385427</v>
+      </c>
+      <c r="L18" s="55" t="n">
+        <v>93.636460554371</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -2118,35 +2120,35 @@
           <t>(Inventories * 365) / Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="C19" s="53" t="n">
-        <v>12.16666666666667</v>
-      </c>
-      <c r="D19" s="53" t="n">
-        <v>11.71183800623053</v>
-      </c>
-      <c r="E19" s="53" t="n">
-        <v>11.27401228637144</v>
-      </c>
-      <c r="F19" s="53" t="n">
-        <v>10.8525538831426</v>
-      </c>
-      <c r="G19" s="53" t="n">
-        <v>10.44685093424008</v>
-      </c>
-      <c r="H19" s="53" t="n">
-        <v>10.05631445071708</v>
-      </c>
-      <c r="I19" s="53" t="n">
-        <v>9.680377461913338</v>
-      </c>
-      <c r="J19" s="53" t="n">
-        <v>9.318494192302358</v>
-      </c>
-      <c r="K19" s="53" t="n">
-        <v>8.970139269223811</v>
-      </c>
-      <c r="L19" s="53" t="n">
-        <v>8.634806960099661</v>
+      <c r="C19" s="58" t="n">
+        <v>25.06452104942038</v>
+      </c>
+      <c r="D19" s="58" t="n">
+        <v>23.23531128688596</v>
+      </c>
+      <c r="E19" s="58" t="n">
+        <v>25.3338721873126</v>
+      </c>
+      <c r="F19" s="58" t="n">
+        <v>17.54824050337917</v>
+      </c>
+      <c r="G19" s="58" t="n">
+        <v>15.01095967706932</v>
+      </c>
+      <c r="H19" s="58" t="n">
+        <v>18.42050850053607</v>
+      </c>
+      <c r="I19" s="58" t="n">
+        <v>21.80095770151636</v>
+      </c>
+      <c r="J19" s="58" t="n">
+        <v>13.85451619270304</v>
+      </c>
+      <c r="K19" s="58" t="n">
+        <v>14.93705642658607</v>
+      </c>
+      <c r="L19" s="58" t="n">
+        <v>3.898054217759106</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -2179,34 +2181,34 @@
         </is>
       </c>
       <c r="C21" s="42" t="n">
-        <v>0.4</v>
+        <v>0.6157993436474449</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>0.4037037037037037</v>
+        <v>0.6191106170094497</v>
       </c>
       <c r="E21" s="42" t="n">
-        <v>0.4074417009602195</v>
+        <v>0.652473722363175</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>0.4112143093024437</v>
+        <v>0.6590195720063889</v>
       </c>
       <c r="G21" s="42" t="n">
-        <v>0.4150218492033923</v>
+        <v>0.6778100199279796</v>
       </c>
       <c r="H21" s="42" t="n">
-        <v>0.4188646441034237</v>
+        <v>0.689258007710247</v>
       </c>
       <c r="I21" s="42" t="n">
-        <v>0.4227430204377147</v>
+        <v>0.684016744842891</v>
       </c>
       <c r="J21" s="42" t="n">
-        <v>0.4266573076640087</v>
+        <v>0.6892008588349102</v>
       </c>
       <c r="K21" s="42" t="n">
-        <v>0.4306078382905165</v>
+        <v>0.6976444382797138</v>
       </c>
       <c r="L21" s="42" t="n">
-        <v>0.4345949479042934</v>
+        <v>0.6882374238616519</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -2221,34 +2223,34 @@
         </is>
       </c>
       <c r="C22" s="39" t="n">
-        <v>0.235</v>
+        <v>0.236544772620722</v>
       </c>
       <c r="D22" s="39" t="n">
-        <v>0.2415277777777778</v>
+        <v>0.2482045580878266</v>
       </c>
       <c r="E22" s="39" t="n">
-        <v>0.2482368827160494</v>
+        <v>0.3176694454512505</v>
       </c>
       <c r="F22" s="39" t="n">
-        <v>0.2551323516803841</v>
+        <v>0.3413698020549415</v>
       </c>
       <c r="G22" s="39" t="n">
-        <v>0.2622193614492836</v>
+        <v>0.3703038142852149</v>
       </c>
       <c r="H22" s="39" t="n">
-        <v>0.2695032326006526</v>
+        <v>0.415948788729713</v>
       </c>
       <c r="I22" s="39" t="n">
-        <v>0.2769894335062358</v>
+        <v>0.4205527815604983</v>
       </c>
       <c r="J22" s="39" t="n">
-        <v>0.28468358443696</v>
+        <v>0.417728806361041</v>
       </c>
       <c r="K22" s="39" t="n">
-        <v>0.2925914617824345</v>
+        <v>0.4464429957327372</v>
       </c>
       <c r="L22" s="39" t="n">
-        <v>0.3007190023875017</v>
+        <v>0.4562195624085985</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -2263,34 +2265,34 @@
         </is>
       </c>
       <c r="C23" s="42" t="n">
-        <v>0.19</v>
+        <v>0.196882325363338</v>
       </c>
       <c r="D23" s="42" t="n">
-        <v>0.1935185185185185</v>
+        <v>0.2357309616453585</v>
       </c>
       <c r="E23" s="42" t="n">
-        <v>0.19710219478738</v>
+        <v>0.1501540413193186</v>
       </c>
       <c r="F23" s="42" t="n">
-        <v>0.2007522354315907</v>
+        <v>0.3118171054409065</v>
       </c>
       <c r="G23" s="42" t="n">
-        <v>0.2044698694210646</v>
+        <v>0.3096248645247002</v>
       </c>
       <c r="H23" s="42" t="n">
-        <v>0.2082563484844177</v>
+        <v>0.3645173956498977</v>
       </c>
       <c r="I23" s="42" t="n">
-        <v>0.2121129475304254</v>
+        <v>0.3668633681343622</v>
       </c>
       <c r="J23" s="42" t="n">
-        <v>0.2160409650772876</v>
+        <v>0.3414623787839464</v>
       </c>
       <c r="K23" s="42" t="n">
-        <v>0.2200417236898252</v>
+        <v>0.3595597294408499</v>
       </c>
       <c r="L23" s="42" t="n">
-        <v>0.2241165704248222</v>
+        <v>0.3614601524896707</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -2305,34 +2307,34 @@
         </is>
       </c>
       <c r="C24" s="39" t="n">
-        <v>0.1085714285714286</v>
+        <v>0.0867244209939389</v>
       </c>
       <c r="D24" s="39" t="n">
-        <v>0.1126684636118598</v>
+        <v>0.0879520171225206</v>
       </c>
       <c r="E24" s="39" t="n">
-        <v>0.1169201037481564</v>
+        <v>0.06401826554580294</v>
       </c>
       <c r="F24" s="39" t="n">
-        <v>0.1213321831348793</v>
+        <v>0.136936584821117</v>
       </c>
       <c r="G24" s="39" t="n">
-        <v>0.1259107560833653</v>
+        <v>0.1469611132683507</v>
       </c>
       <c r="H24" s="39" t="n">
-        <v>0.1306621053695301</v>
+        <v>0.1835675701586978</v>
       </c>
       <c r="I24" s="39" t="n">
-        <v>0.1355927508551727</v>
+        <v>0.1993695866681285</v>
       </c>
       <c r="J24" s="39" t="n">
-        <v>0.1407094584346121</v>
+        <v>0.175643726819038</v>
       </c>
       <c r="K24" s="39" t="n">
-        <v>0.1460192493189394</v>
+        <v>0.172085839859576</v>
       </c>
       <c r="L24" s="39" t="n">
-        <v>0.1515294096705968</v>
+        <v>0.1645097035070912</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -2347,34 +2349,34 @@
         </is>
       </c>
       <c r="C25" s="42" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.2333152770254316</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>0.4300411522633745</v>
+        <v>0.2467044410057127</v>
       </c>
       <c r="E25" s="42" t="n">
-        <v>0.4380048773052888</v>
+        <v>0.2003312459198723</v>
       </c>
       <c r="F25" s="42" t="n">
-        <v>0.4461160787368683</v>
+        <v>0.3834652594547054</v>
       </c>
       <c r="G25" s="42" t="n">
-        <v>0.4543774876023658</v>
+        <v>0.374298417635921</v>
       </c>
       <c r="H25" s="42" t="n">
-        <v>0.4627918855209281</v>
+        <v>0.4315223821731414</v>
       </c>
       <c r="I25" s="42" t="n">
-        <v>0.4713621056231676</v>
+        <v>0.4367546925099975</v>
       </c>
       <c r="J25" s="42" t="n">
-        <v>0.4800910335050681</v>
+        <v>0.3508871464385641</v>
       </c>
       <c r="K25" s="42" t="n">
-        <v>0.4889816081996146</v>
+        <v>0.3282813797829982</v>
       </c>
       <c r="L25" s="42" t="n">
-        <v>0.4980368231662731</v>
+        <v>0.2964722734140952</v>
       </c>
     </row>
   </sheetData>
@@ -2425,34 +2427,34 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -2479,34 +2481,34 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>200000000000</v>
+        <v>85320000000</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>216000000000</v>
+        <v>89950000000</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>233280000000</v>
+        <v>110360000000</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>251942400000</v>
+        <v>125843000000</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>272097792000</v>
+        <v>143015000000</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>293865615360</v>
+        <v>168088000000</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>317374864588.8</v>
+        <v>198270000000</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>342764853755.9</v>
+        <v>211915000000</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>370186042056.38</v>
+        <v>245122000000</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>399800925420.89</v>
+        <v>281724000000</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -2516,34 +2518,34 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>120000000000</v>
+        <v>32780000000</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>128400000000</v>
+        <v>34261000000</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>137388000000</v>
+        <v>38353000000</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>147005160000</v>
+        <v>42910000000</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>157295521200</v>
+        <v>46078000000</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>168306207684</v>
+        <v>52232000000</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>180087642221.88</v>
+        <v>62650000000</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>192693777177.41</v>
+        <v>65863000000</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>206182341579.83</v>
+        <v>74114000000</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>220615105490.42</v>
+        <v>87831000000</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -2553,34 +2555,34 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>80000000000</v>
+        <v>52540000000</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>87200000000</v>
+        <v>55689000000</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>95048000000</v>
+        <v>72007000000</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>103602320000</v>
+        <v>82933000000</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>112926528800</v>
+        <v>96937000000</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>123089916392</v>
+        <v>115856000000</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>134168008867.28</v>
+        <v>135620000000</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>146243129665.34</v>
+        <v>146052000000</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>159405011335.22</v>
+        <v>171008000000</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>173751462355.38</v>
+        <v>193893000000</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -2607,34 +2609,34 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>15000000000</v>
+        <v>11988000000</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>16500000000</v>
+        <v>13037000000</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>18150000000</v>
+        <v>14726000000</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>19965000000</v>
+        <v>16876000000</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>21961500000</v>
+        <v>19269000000</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>24157650000</v>
+        <v>20716000000</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>26573415000</v>
+        <v>24512000000</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>29230756500</v>
+        <v>27195000000</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>32153832150</v>
+        <v>29510000000</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>35369215365</v>
+        <v>32488000000</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -2644,34 +2646,34 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>18000000000</v>
+        <v>19198000000</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>18900000000</v>
+        <v>20116000000</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>19845000000</v>
+        <v>22223000000</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>20837250000</v>
+        <v>23098000000</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>21879112500</v>
+        <v>24709000000</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>22973068125</v>
+        <v>25224000000</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>24121721531.25</v>
+        <v>27725000000</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>25327807607.81</v>
+        <v>29589000000</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>26594197988.2</v>
+        <v>32065000000</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>27923907887.61</v>
+        <v>32877000000</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -2681,34 +2683,34 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>33000000000</v>
+        <v>31186000000</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>35310000000</v>
+        <v>33153000000</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>37781700000</v>
+        <v>36949000000</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>40426419000</v>
+        <v>39974000000</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>43256268330</v>
+        <v>43978000000</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>46284207113.1</v>
+        <v>45940000000</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>49524101611.02</v>
+        <v>52237000000</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>52990788723.79</v>
+        <v>56784000000</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>56700143934.45</v>
+        <v>61575000000</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>60669154009.87</v>
+        <v>65365000000</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -2718,34 +2720,34 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>47000000000</v>
+        <v>20182000000</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>52170000000</v>
+        <v>22326000000</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>57908700000</v>
+        <v>35058000000</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>64278657000</v>
+        <v>42959000000</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>71349309270</v>
+        <v>52959000000</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>79197733289.7</v>
+        <v>69916000000</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>87909483951.57001</v>
+        <v>83383000000</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>97579527186.24001</v>
+        <v>88523000000</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>108313275176.73</v>
+        <v>109433000000</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>120227735446.17</v>
+        <v>128528000000</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -2771,16 +2773,36 @@
           <t xml:space="preserve">    Total Non-Operating Income / (Expense)</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
+      <c r="B14" s="9" t="n">
+        <v>-223000000</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>575000000</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>1416000000</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>729000000</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>77000000</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>1186000000</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>333000000</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>788000000</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>-1646000000</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>-1228000000</v>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
@@ -2788,16 +2810,36 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
+      <c r="B15" s="11" t="n">
+        <v>1243000000</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>1567000000</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>2234000000</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>2772000000</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>2591000000</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>2346000000</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>2063000000</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>1968000000</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>2935000000</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>2800000000</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -2805,16 +2847,36 @@
           <t xml:space="preserve">    Income Before Income Taxes</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="13" t="n"/>
+      <c r="B16" s="13" t="n">
+        <v>25639000000</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>29901000000</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>36474000000</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>43688000000</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>53036000000</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>71102000000</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>83716000000</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>89311000000</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>107787000000</v>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>124500000000</v>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -2822,16 +2884,36 @@
           <t xml:space="preserve">    Income Tax Expense / (Benefit)</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="11" t="n"/>
-      <c r="K17" s="11" t="n"/>
+      <c r="B17" s="11" t="n">
+        <v>5100000000</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>4412000000</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>19903000000</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>4448000000</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>8755000000</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>9831000000</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>10978000000</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>16950000000</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>19651000000</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>22668000000</v>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
@@ -2840,34 +2922,34 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>38000000000</v>
+        <v>16798000000</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>41800000000</v>
+        <v>21204000000</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>45980000000</v>
+        <v>16571000000</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>50578000000</v>
+        <v>39240000000</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>55635800000</v>
+        <v>44281000000</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>61199380000</v>
+        <v>61271000000</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>67319318000</v>
+        <v>72738000000</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>74051249800</v>
+        <v>72361000000</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>81456374780</v>
+        <v>88136000000</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>89602012258</v>
+        <v>101832000000</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -2893,16 +2975,36 @@
           <t xml:space="preserve">    Basic Earnings Per Share (USD)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="16" t="n"/>
-      <c r="I20" s="16" t="n"/>
-      <c r="J20" s="16" t="n"/>
-      <c r="K20" s="16" t="n"/>
+      <c r="B20" s="16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="J20" s="16" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="K20" s="16" t="n">
+        <v>13.71</v>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -2911,34 +3013,34 @@
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="D21" s="17" t="n">
-        <v>3.14</v>
+        <v>2.13</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>3.51</v>
+        <v>5.06</v>
       </c>
       <c r="F21" s="17" t="n">
-        <v>3.93</v>
+        <v>5.76</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>4.41</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H21" s="17" t="n">
-        <v>4.93</v>
+        <v>9.65</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>5.53</v>
+        <v>9.68</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>6.19</v>
+        <v>11.8</v>
       </c>
       <c r="K21" s="17" t="n">
-        <v>6.93</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -2947,16 +3049,36 @@
           <t xml:space="preserve">    Weighted Average Shares (Basic)</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+      <c r="B22" s="9" t="n">
+        <v>7925000000</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>7746000000</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>7700000000</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>7673000000</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>7610000000</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>7547000000</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>7496000000</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>7446000000</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>7432000000</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>7430000000</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -2965,34 +3087,34 @@
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>16000000000</v>
+        <v>8013000000</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>15680000000</v>
+        <v>7832000000</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>15366400000</v>
+        <v>7794000000</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>15059072000</v>
+        <v>7753000000</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>14757890560</v>
+        <v>7683000000</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>14462732748.8</v>
+        <v>7608000000</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>14173478093.82</v>
+        <v>7558000000</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>13890008531.95</v>
+        <v>7472000000</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>13612208361.31</v>
+        <v>7469000000</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>13339964194.08</v>
+        <v>7482000000</v>
       </c>
     </row>
   </sheetData>
@@ -3043,34 +3165,34 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -3097,34 +3219,34 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>30000000000</v>
+        <v>6510000000</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>31200000000</v>
+        <v>7663000000</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>32448000000</v>
+        <v>11946000000</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>33745920000</v>
+        <v>11356000000</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>35095756800</v>
+        <v>13576000000</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>36499587072</v>
+        <v>14224000000</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>37959570554.88</v>
+        <v>13931000000</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>39477953377.08</v>
+        <v>34704000000</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>41057071512.16</v>
+        <v>18300000000</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>42699354372.64</v>
+        <v>30242000000</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -3134,34 +3256,34 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>25000000000</v>
+        <v>106730000000</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>26250000000</v>
+        <v>125318000000</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>27562500000</v>
+        <v>121822000000</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>28940625000</v>
+        <v>122463000000</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>30387656250</v>
+        <v>122951000000</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>31907039062.5</v>
+        <v>116110000000</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>33502391015.63</v>
+        <v>90818000000</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>35177510566.41</v>
+        <v>76558000000</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>36936386094.73</v>
+        <v>57244000000</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>38783205399.46</v>
+        <v>64323000000</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -3171,34 +3293,34 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>22000000000</v>
+        <v>18277000000</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>23320000000</v>
+        <v>19792000000</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>24719200000</v>
+        <v>26481000000</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>26202352000</v>
+        <v>29524000000</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>27774493120</v>
+        <v>32011000000</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>29440962707.2</v>
+        <v>38043000000</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>31207420469.63</v>
+        <v>44261000000</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>33079865697.81</v>
+        <v>48688000000</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>35064657639.68</v>
+        <v>57868000000</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>37168537098.06</v>
+        <v>69905000000</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -3208,34 +3330,34 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>4000000000</v>
+        <v>2251000000</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>4120000000</v>
+        <v>2181000000</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>4243600000</v>
+        <v>2662000000</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>4370908000</v>
+        <v>2063000000</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>4502035240</v>
+        <v>1895000000</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>4637096297.2</v>
+        <v>2636000000</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>4776209186.12</v>
+        <v>3742000000</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>4919495461.7</v>
+        <v>2500000000</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>5067080325.55</v>
+        <v>3033000000</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>5219092735.32</v>
+        <v>938000000</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -3244,16 +3366,36 @@
           <t xml:space="preserve">    Other Current Assets</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
+      <c r="B9" s="11" t="n">
+        <v>5892000000</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>4897000000</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>6764000000</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>10146000000</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>11482000000</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>13446000000</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>19527000000</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>21807000000</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>23289000000</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>25723000000</v>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -3262,34 +3404,34 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>100000000000</v>
+        <v>139660000000</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>106000000000</v>
+        <v>159851000000</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>112360000000</v>
+        <v>169675000000</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>119101600000</v>
+        <v>175552000000</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>126247696000</v>
+        <v>181915000000</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>133822557760</v>
+        <v>184459000000</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>141851911225.6</v>
+        <v>172279000000</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>150363025899.14</v>
+        <v>184257000000</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>159384807453.08</v>
+        <v>159734000000</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>168947895900.27</v>
+        <v>191131000000</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -3316,34 +3458,34 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>45000000000</v>
+        <v>18356000000</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>47250000000</v>
+        <v>23734000000</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>49612500000</v>
+        <v>29460000000</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>52093125000</v>
+        <v>36477000000</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>54697781250</v>
+        <v>44151000000</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>57432670312.5</v>
+        <v>52903000000</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>60304303828.13</v>
+        <v>74059000000</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>63319519019.53</v>
+        <v>95641000000</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>66485494970.51</v>
+        <v>135591000000</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>69809769719.03</v>
+        <v>204966000000</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -3352,16 +3494,36 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="11" t="n"/>
+      <c r="B13" s="11" t="n">
+        <v>17872000000</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>35122000000</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>35389000000</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>42026000000</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>43351000000</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>49711000000</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>67524000000</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>67886000000</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>119220000000</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>119509000000</v>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -3369,16 +3531,36 @@
           <t xml:space="preserve">    Intangible Assets, Net</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
+      <c r="B14" s="9" t="n">
+        <v>3733000000</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>10106000000</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>8053000000</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>7750000000</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>7038000000</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>7800000000</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>11298000000</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>9366000000</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>27597000000</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>22604000000</v>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
@@ -3386,16 +3568,36 @@
           <t xml:space="preserve">    Marketable Securities (Non-Current)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
+      <c r="B15" s="11" t="n">
+        <v>10438000000</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>6023000000</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>1862000000</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>2649000000</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>3188000000</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>5984000000</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>6891000000</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>9876000000</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>14210000000</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>14850000000</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -3403,16 +3605,36 @@
           <t xml:space="preserve">    Other Non-Current Assets</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>3610000000</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>6250000000</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>4409000000</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>22102000000</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>21668000000</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>32922000000</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>32789000000</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>44950000000</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>55811000000</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>65943000000</v>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
@@ -3421,34 +3643,34 @@
         </is>
       </c>
       <c r="B17" s="19" t="n">
-        <v>350000000000</v>
+        <v>193694000000</v>
       </c>
       <c r="C17" s="19" t="n">
-        <v>371000000000</v>
+        <v>241086000000</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>393260000000</v>
+        <v>258848000000</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>416855600000</v>
+        <v>286556000000</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>441866936000</v>
+        <v>301311000000</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>468378952160</v>
+        <v>333779000000</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>496481689289.6</v>
+        <v>364840000000</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>526270590646.98</v>
+        <v>411976000000</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>557846826085.79</v>
+        <v>512163000000</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>591317635650.9399</v>
+        <v>619003000000</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -3475,34 +3697,34 @@
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>40000000000</v>
+        <v>6316000000</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>42000000000</v>
+        <v>8610000000</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>44100000000</v>
+        <v>10592000000</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>46305000000</v>
+        <v>9382000000</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>48620250000</v>
+        <v>12530000000</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>51051262500</v>
+        <v>15163000000</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>53603825625</v>
+        <v>19000000000</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>56284016906.25</v>
+        <v>18095000000</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>59098217751.56</v>
+        <v>21996000000</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>62053128639.14</v>
+        <v>27724000000</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -3511,16 +3733,36 @@
           <t xml:space="preserve">    Accrued Liabilities</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
+      <c r="B20" s="9" t="n">
+        <v>20387000000</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>22452000000</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>28195000000</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>9351000000</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>10011000000</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>11612000000</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>13179000000</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>13865000000</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>17294000000</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>18920000000</v>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -3528,16 +3770,36 @@
           <t xml:space="preserve">    Deferred Revenue (Current)</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="11" t="n"/>
-      <c r="K21" s="11" t="n"/>
+      <c r="B21" s="11" t="n">
+        <v>20292000000</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>23907000000</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>28905000000</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>32676000000</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>36000000000</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>41459000000</v>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>45538000000</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>50901000000</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>57582000000</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>64555000000</v>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -3545,16 +3807,36 @@
           <t xml:space="preserve">    Commercial Paper and Short-Term Debt</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+      <c r="B22" s="9" t="n">
+        <v>12722000000</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>12765000000</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>7984000000</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>10895000000</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>13709000000</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>8049000000</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>17365000000</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>21288000000</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>28414000000</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>30019000000</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
@@ -3563,34 +3845,34 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>95000000000</v>
+        <v>59717000000</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>99750000000</v>
+        <v>67734000000</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>104737500000</v>
+        <v>75676000000</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>109974375000</v>
+        <v>62304000000</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>115473093750</v>
+        <v>72250000000</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>121246748437.5</v>
+        <v>76283000000</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>127309085859.38</v>
+        <v>95082000000</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>133674540152.34</v>
+        <v>104149000000</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>140358267159.96</v>
+        <v>125286000000</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>147376180517.96</v>
+        <v>141218000000</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -3617,34 +3899,34 @@
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>85000000000</v>
+        <v>52714000000</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>86700000000</v>
+        <v>76083000000</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>88434000000</v>
+        <v>72242000000</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>90202680000</v>
+        <v>66662000000</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>92006733600</v>
+        <v>59990000000</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>93846868272</v>
+        <v>48088000000</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>95723805637.44</v>
+        <v>47032000000</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>97638281750.19</v>
+        <v>41990000000</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>99591047385.19</v>
+        <v>42688000000</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>101582868332.9</v>
+        <v>40152000000</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -3653,16 +3935,36 @@
           <t xml:space="preserve">    Deferred Revenue (Non-Current)</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
+      <c r="B26" s="9" t="n">
+        <v>2788000000</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>2752000000</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>2813000000</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>4530000000</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>3180000000</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>2810000000</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>2870000000</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>2912000000</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>2602000000</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>2710000000</v>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -3670,16 +3972,36 @@
           <t xml:space="preserve">    Other Non-Current Liabilities</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="11" t="n"/>
-      <c r="I27" s="11" t="n"/>
-      <c r="J27" s="11" t="n"/>
-      <c r="K27" s="11" t="n"/>
+      <c r="B27" s="11" t="n">
+        <v>6282000000</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>8568000000</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>25400000000</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>50730000000</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>47587000000</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>64610000000</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>53314000000</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>56652000000</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>73110000000</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>91444000000</v>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
@@ -3688,34 +4010,34 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>260000000000</v>
+        <v>121501000000</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>270400000000</v>
+        <v>155137000000</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>281216000000</v>
+        <v>176130000000</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>292464640000</v>
+        <v>184226000000</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>304163225600</v>
+        <v>183007000000</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>316329754624</v>
+        <v>191791000000</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>328982944808.96</v>
+        <v>198298000000</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>342142262601.32</v>
+        <v>205753000000</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>355827953105.37</v>
+        <v>243686000000</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>370061071229.59</v>
+        <v>275524000000</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -3742,34 +4064,34 @@
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>50000000000</v>
+        <v>68178000000</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>51500000000</v>
+        <v>69315000000</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>53045000000</v>
+        <v>71223000000</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>54636350000</v>
+        <v>78520000000</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>56275440500</v>
+        <v>80552000000</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>57963703715</v>
+        <v>83111000000</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>59702614826.45</v>
+        <v>86939000000</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>61493693271.24</v>
+        <v>93718000000</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>63338504069.38</v>
+        <v>100923000000</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>65238659191.46</v>
+        <v>108520000000</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -3778,16 +4100,36 @@
           <t xml:space="preserve">    Additional Paid-in Capital</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="11" t="n"/>
-      <c r="I31" s="11" t="n"/>
-      <c r="J31" s="11" t="n"/>
-      <c r="K31" s="11" t="n"/>
+      <c r="B31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
@@ -3795,16 +4137,36 @@
           <t xml:space="preserve">    Retained Earnings / (Accumulated Deficit)</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n"/>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="9" t="n"/>
-      <c r="K32" s="9" t="n"/>
+      <c r="B32" s="9" t="n">
+        <v>2282000000</v>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>17769000000</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>13682000000</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>24150000000</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>34566000000</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>57055000000</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>84281000000</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>118848000000</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>173144000000</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>240650000000</v>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
@@ -3812,16 +4174,36 @@
           <t xml:space="preserve">    Accumulated Other Comprehensive Income / (Loss)</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="11" t="n"/>
-      <c r="J33" s="11" t="n"/>
-      <c r="K33" s="11" t="n"/>
+      <c r="B33" s="11" t="n">
+        <v>1533000000</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>-1198000000</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>-2187000000</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>-340000000</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>3186000000</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>1822000000</v>
+      </c>
+      <c r="H33" s="11" t="n">
+        <v>-4678000000</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>-6343000000</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>-5590000000</v>
+      </c>
+      <c r="K33" s="11" t="n">
+        <v>-5691000000</v>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
@@ -3830,34 +4212,34 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>90000000000</v>
+        <v>71997000000</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>97200000000</v>
+        <v>85949000000</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>104976000000</v>
+        <v>82718000000</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>113374080000</v>
+        <v>102330000000</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>122444006400</v>
+        <v>118304000000</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>132239526912</v>
+        <v>141988000000</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>142818689064.96</v>
+        <v>166542000000</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>154244184190.16</v>
+        <v>206223000000</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>166583718925.37</v>
+        <v>268477000000</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>179910416439.4</v>
+        <v>343479000000</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -3867,34 +4249,34 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>350000000000</v>
+        <v>193694000000</v>
       </c>
       <c r="C35" s="19" t="n">
-        <v>371000000000</v>
+        <v>241086000000</v>
       </c>
       <c r="D35" s="19" t="n">
-        <v>393260000000</v>
+        <v>258848000000</v>
       </c>
       <c r="E35" s="19" t="n">
-        <v>416855600000</v>
+        <v>286556000000</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>441866936000</v>
+        <v>301311000000</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>468378952160</v>
+        <v>333779000000</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>496481689289.6</v>
+        <v>364840000000</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>526270590646.98</v>
+        <v>411976000000</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>557846826085.79</v>
+        <v>512163000000</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>591317635650.9399</v>
+        <v>619003000000</v>
       </c>
     </row>
   </sheetData>
@@ -3945,34 +4327,34 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -3999,34 +4381,34 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>38000000000</v>
+        <v>16798000000</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>41800000000</v>
+        <v>21204000000</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>45980000000</v>
+        <v>16571000000</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>50578000000</v>
+        <v>39240000000</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>55635800000</v>
+        <v>44281000000</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>61199380000</v>
+        <v>61271000000</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>67319318000</v>
+        <v>72738000000</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>74051249800</v>
+        <v>72361000000</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>81456374780</v>
+        <v>88136000000</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>89602012258</v>
+        <v>101832000000</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -4036,34 +4418,34 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>11000000000</v>
+        <v>6622000000</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>11550000000</v>
+        <v>8778000000</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>12127500000</v>
+        <v>10261000000</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>12733875000</v>
+        <v>11600000000</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>13370568750</v>
+        <v>12796000000</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>14039097187.5</v>
+        <v>11686000000</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>14741052046.88</v>
+        <v>14460000000</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>15478104649.22</v>
+        <v>13861000000</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>16252009881.68</v>
+        <v>15000000000</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>17064610375.76</v>
+        <v>17200000000</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -4073,34 +4455,34 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>8000000000</v>
+        <v>2668000000</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>8640000000</v>
+        <v>3266000000</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>9331200000</v>
+        <v>3940000000</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>10077696000</v>
+        <v>4652000000</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>10883911680</v>
+        <v>5289000000</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>11754624614.4</v>
+        <v>6118000000</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>12694994583.55</v>
+        <v>7502000000</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>13710594150.24</v>
+        <v>9611000000</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>14807441682.26</v>
+        <v>10735000000</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>15992037016.84</v>
+        <v>12500000000</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -4109,16 +4491,36 @@
           <t xml:space="preserve">    Deferred Income Taxes</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>-1532000000</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>-180000000</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>5518000000</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>-2521000000</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>-11000000</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>-150000000</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>-5702000000</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>-6059000000</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>-3899000000</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>-2100000000</v>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -4126,16 +4528,36 @@
           <t xml:space="preserve">    Change in Accounts Receivable</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
+      <c r="B9" s="11" t="n">
+        <v>530000000</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>-1216000000</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>-3862000000</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>-2812000000</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>-2577000000</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>-6481000000</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>-6834000000</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>-4068000000</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>-7825000000</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>-8200000000</v>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -4143,16 +4565,36 @@
           <t xml:space="preserve">    Change in Inventories</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
+      <c r="B10" s="9" t="n">
+        <v>600000000</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>-50000000</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>-465000000</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>597000000</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>168000000</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>-737000000</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>-1123000000</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>1242000000</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>-533000000</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>1562000000</v>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
@@ -4160,16 +4602,36 @@
           <t xml:space="preserve">    Change in Accounts Payable</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="n"/>
+      <c r="B11" s="11" t="n">
+        <v>88000000</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>390000000</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>2928000000</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>232000000</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>2330000000</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>2798000000</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>2943000000</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>-2725000000</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>3326000000</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>4200000000</v>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -4178,34 +4640,34 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>70000000000</v>
+        <v>33325000000</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>76300000000</v>
+        <v>39507000000</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>83167000000</v>
+        <v>43884000000</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>90652030000</v>
+        <v>52185000000</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>98810712700</v>
+        <v>60675000000</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>107703676843</v>
+        <v>76740000000</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>117397007758.87</v>
+        <v>89035000000</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>127962738457.17</v>
+        <v>87582000000</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>139479384918.31</v>
+        <v>118548000000</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>152032529560.96</v>
+        <v>136162000000</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -4232,34 +4694,34 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>12000000000</v>
+        <v>-8322000000</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>12720000000</v>
+        <v>-11632000000</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>13483200000</v>
+        <v>-11632000000</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>14292192000</v>
+        <v>-13925000000</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>15149723520</v>
+        <v>-15441000000</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>16058706931.2</v>
+        <v>-20622000000</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>17022229347.07</v>
+        <v>-23886000000</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>18043563107.9</v>
+        <v>-28107000000</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>19126176894.37</v>
+        <v>-44477000000</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>20273747508.03</v>
+        <v>-64551000000</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -4268,16 +4730,36 @@
           <t xml:space="preserve">    Purchases of Marketable Securities</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
+      <c r="B15" s="11" t="n">
+        <v>-104893000000</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>-137380000000</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>-176905000000</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>-57697000000</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>-77190000000</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>-62924000000</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>-26456000000</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>-37651000000</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>-17732000000</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>-22100000000</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -4285,16 +4767,36 @@
           <t xml:space="preserve">    Proceeds from Sales/Maturities of Marketable Securities</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>106359000000</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>125238000000</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>166090000000</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>68060000000</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>84177000000</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>65800000000</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>44840000000</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>47763000000</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>28148000000</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>31200000000</v>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -4302,16 +4804,36 @@
           <t xml:space="preserve">    Payments for Business Acquisitions, Net</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="11" t="n"/>
-      <c r="K17" s="11" t="n"/>
+      <c r="B17" s="11" t="n">
+        <v>-1395000000</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>-25944000000</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>-2888000000</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>-2388000000</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>-2521000000</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>-8909000000</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>-22038000000</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>-1670000000</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>-68840000000</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>-1500000000</v>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -4320,34 +4842,34 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>-15000000000</v>
+        <v>-8251000000</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>-15750000000</v>
+        <v>-49768000000</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>-16537500000</v>
+        <v>-25375000000</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>-17364375000</v>
+        <v>-5860000000</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>-18232593750</v>
+        <v>-10895000000</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>-19144223437.5</v>
+        <v>-26685000000</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>-20101434609.38</v>
+        <v>-27490000000</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>-21106506339.84</v>
+        <v>-19665000000</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>-22161831656.84</v>
+        <v>-102801000000</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>-23269923239.68</v>
+        <v>-56951000000</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -4374,34 +4896,34 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>45000000000</v>
+        <v>-15969000000</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>48150000000</v>
+        <v>-11788000000</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>51520500000</v>
+        <v>-10721000000</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>55126935000</v>
+        <v>-19543000000</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>58985820450</v>
+        <v>-19645000000</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>63114827881.5</v>
+        <v>-27385000000</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>67532865833.21</v>
+        <v>-32696000000</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>72260166441.53</v>
+        <v>-22245000000</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>77318378092.44</v>
+        <v>-17254000000</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>82730664558.91</v>
+        <v>-18420000000</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -4411,34 +4933,34 @@
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>14000000000</v>
+        <v>-11006000000</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>14560000000</v>
+        <v>-11845000000</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>15142400000</v>
+        <v>-12699000000</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>15748096000</v>
+        <v>-13811000000</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>16378019840</v>
+        <v>-15137000000</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>17033140633.6</v>
+        <v>-16521000000</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>17714466258.94</v>
+        <v>-18135000000</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>18423044909.3</v>
+        <v>-19800000000</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>19159966705.67</v>
+        <v>-21771000000</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>19926365373.9</v>
+        <v>-24082000000</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -4447,16 +4969,36 @@
           <t xml:space="preserve">    Proceeds from Issuance of Common Stock</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+      <c r="B22" s="9" t="n">
+        <v>668000000</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>772000000</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>1002000000</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>1142000000</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>1343000000</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>1693000000</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>1841000000</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>1866000000</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>2145000000</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>2450000000</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -4464,16 +5006,36 @@
           <t xml:space="preserve">    Proceeds from Issuance of Long-Term Debt</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="11" t="n"/>
-      <c r="J23" s="11" t="n"/>
-      <c r="K23" s="11" t="n"/>
+      <c r="B23" s="11" t="n">
+        <v>13884000000</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>44344000000</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>7183000000</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>24395000000</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -4481,16 +5043,36 @@
           <t xml:space="preserve">    Repayments of Long-Term Debt</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
+      <c r="B24" s="9" t="n">
+        <v>-3888000000</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>-7922000000</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>-4005000000</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>-3553000000</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>-5055000000</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>-3750000000</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>-9023000000</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>-2750000000</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>-29070000000</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>-2850000000</v>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -4499,34 +5081,34 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>-50000000000</v>
+        <v>-16341000000</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>-53000000000</v>
+        <v>13611000000</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>-56180000000</v>
+        <v>-19216000000</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-59550800000</v>
+        <v>-35772000000</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>-63123848000</v>
+        <v>-38446000000</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>-66911278880</v>
+        <v>-45963000000</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-70925955612.8</v>
+        <v>-58013000000</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>-75181512949.57001</v>
+        <v>-42929000000</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>-79692403726.53999</v>
+        <v>-41555000000</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>-84473947950.13</v>
+        <v>-42902000000</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -4552,16 +5134,36 @@
           <t xml:space="preserve">    Net Increase / (Decrease) in Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="7" t="n"/>
+      <c r="B27" s="7" t="n">
+        <v>8733000000</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>3350000000</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>-707000000</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>10553000000</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>11334000000</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>4092000000</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>3532000000</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>24988000000</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>-25808000000</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>36309000000</v>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -4570,34 +5172,34 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>30000000000</v>
+        <v>10978000000</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>31200000000</v>
+        <v>19711000000</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>32448000000</v>
+        <v>23061000000</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>33745920000</v>
+        <v>22354000000</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>35095756800</v>
+        <v>32907000000</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>36499587072</v>
+        <v>44241000000</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>37959570554.88</v>
+        <v>48333000000</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>39477953377.08</v>
+        <v>51865000000</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>41057071512.16</v>
+        <v>76853000000</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>42699354372.64</v>
+        <v>51045000000</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -4607,34 +5209,34 @@
         </is>
       </c>
       <c r="B29" s="19" t="n">
-        <v>30000000000</v>
+        <v>19711000000</v>
       </c>
       <c r="C29" s="19" t="n">
-        <v>31200000000</v>
+        <v>23061000000</v>
       </c>
       <c r="D29" s="19" t="n">
-        <v>32448000000</v>
+        <v>22354000000</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>33745920000</v>
+        <v>32907000000</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>35095756800</v>
+        <v>44241000000</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>36499587072</v>
+        <v>48333000000</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>37959570554.88</v>
+        <v>51865000000</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>39477953377.08</v>
+        <v>76853000000</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>41057071512.16</v>
+        <v>51045000000</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>42699354372.64</v>
+        <v>87354000000</v>
       </c>
     </row>
   </sheetData>
@@ -4643,510 +5245,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>MSFT — LOUGHRAN-MCDONALD FINANCIAL SENTIMENT ANALYSIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Item 7 (MD&amp;A) Natural Language Processing — Loughran-McDonald Lexicon (2011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>Fiscal Year</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>Total Words</t>
-        </is>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>Positive Count</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="inlineStr">
-        <is>
-          <t>Negative Count</t>
-        </is>
-      </c>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>Net Score</t>
-        </is>
-      </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>P/N Ratio</t>
-        </is>
-      </c>
-      <c r="G3" s="20" t="inlineStr">
-        <is>
-          <t>Net Sentiment %</t>
-        </is>
-      </c>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>Uncertainty Count</t>
-        </is>
-      </c>
-      <c r="I3" s="20" t="inlineStr">
-        <is>
-          <t>Litigious Count</t>
-        </is>
-      </c>
-      <c r="J3" s="20" t="inlineStr">
-        <is>
-          <t>Strong Modal</t>
-        </is>
-      </c>
-      <c r="K3" s="20" t="inlineStr">
-        <is>
-          <t>Weak Modal</t>
-        </is>
-      </c>
-      <c r="L3" s="20" t="inlineStr">
-        <is>
-          <t>Tone Classification</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="21" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B4" s="22" t="n">
-        <v>6426</v>
-      </c>
-      <c r="C4" s="22" t="n">
-        <v>152</v>
-      </c>
-      <c r="D4" s="22" t="n">
-        <v>289</v>
-      </c>
-      <c r="E4" s="22" t="n">
-        <v>-137</v>
-      </c>
-      <c r="F4" s="23" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="G4" s="24" t="n">
-        <v>-0.02132</v>
-      </c>
-      <c r="H4" s="22" t="n">
-        <v>97</v>
-      </c>
-      <c r="I4" s="22" t="n">
-        <v>32</v>
-      </c>
-      <c r="J4" s="22" t="n">
-        <v>14</v>
-      </c>
-      <c r="K4" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="25" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="26" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B5" s="27" t="n">
-        <v>5965</v>
-      </c>
-      <c r="C5" s="27" t="n">
-        <v>156</v>
-      </c>
-      <c r="D5" s="27" t="n">
-        <v>210</v>
-      </c>
-      <c r="E5" s="27" t="n">
-        <v>-54</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>0.7429</v>
-      </c>
-      <c r="G5" s="29" t="n">
-        <v>-0.009053</v>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>79</v>
-      </c>
-      <c r="I5" s="27" t="n">
-        <v>39</v>
-      </c>
-      <c r="J5" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" s="25" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="21" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B6" s="22" t="n">
-        <v>5674</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <v>170</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <v>159</v>
-      </c>
-      <c r="E6" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <v>1.0692</v>
-      </c>
-      <c r="G6" s="24" t="n">
-        <v>0.001939</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>86</v>
-      </c>
-      <c r="I6" s="22" t="n">
-        <v>38</v>
-      </c>
-      <c r="J6" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="L6" s="30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="26" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B7" s="27" t="n">
-        <v>5962</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>185</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>148</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>37</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G7" s="29" t="n">
-        <v>0.006206000000000001</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>97</v>
-      </c>
-      <c r="I7" s="27" t="n">
-        <v>36</v>
-      </c>
-      <c r="J7" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="K7" s="27" t="n">
-        <v>12</v>
-      </c>
-      <c r="L7" s="30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="21" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B8" s="22" t="n">
-        <v>5076</v>
-      </c>
-      <c r="C8" s="22" t="n">
-        <v>157</v>
-      </c>
-      <c r="D8" s="22" t="n">
-        <v>124</v>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>33</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <v>1.2661</v>
-      </c>
-      <c r="G8" s="24" t="n">
-        <v>0.006501</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>72</v>
-      </c>
-      <c r="I8" s="22" t="n">
-        <v>42</v>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="L8" s="30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="26" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B9" s="27" t="n">
-        <v>5008</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>161</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>104</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>57</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>1.5481</v>
-      </c>
-      <c r="G9" s="29" t="n">
-        <v>0.011382</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>79</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>40</v>
-      </c>
-      <c r="J9" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="K9" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="L9" s="30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="21" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B10" s="22" t="n">
-        <v>5073</v>
-      </c>
-      <c r="C10" s="22" t="n">
-        <v>148</v>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>159</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>-11</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>0.9308</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <v>-0.002168</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>77</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>29</v>
-      </c>
-      <c r="J10" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="K10" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="L10" s="25" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="26" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B11" s="27" t="n">
-        <v>4667</v>
-      </c>
-      <c r="C11" s="27" t="n">
-        <v>134</v>
-      </c>
-      <c r="D11" s="27" t="n">
-        <v>126</v>
-      </c>
-      <c r="E11" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>1.0635</v>
-      </c>
-      <c r="G11" s="29" t="n">
-        <v>0.001714</v>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>70</v>
-      </c>
-      <c r="I11" s="27" t="n">
-        <v>34</v>
-      </c>
-      <c r="J11" s="27" t="n">
-        <v>12</v>
-      </c>
-      <c r="K11" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="21" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B12" s="22" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C12" s="22" t="n">
-        <v>133</v>
-      </c>
-      <c r="D12" s="22" t="n">
-        <v>116</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>1.1466</v>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>0.003953</v>
-      </c>
-      <c r="H12" s="22" t="n">
-        <v>60</v>
-      </c>
-      <c r="I12" s="22" t="n">
-        <v>31</v>
-      </c>
-      <c r="J12" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="K12" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="L12" s="30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="26" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B13" s="27" t="n">
-        <v>4598</v>
-      </c>
-      <c r="C13" s="27" t="n">
-        <v>156</v>
-      </c>
-      <c r="D13" s="27" t="n">
-        <v>134</v>
-      </c>
-      <c r="E13" s="27" t="n">
-        <v>22</v>
-      </c>
-      <c r="F13" s="28" t="n">
-        <v>1.1642</v>
-      </c>
-      <c r="G13" s="29" t="n">
-        <v>0.004785</v>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>62</v>
-      </c>
-      <c r="I13" s="27" t="n">
-        <v>32</v>
-      </c>
-      <c r="J13" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="K13" s="27" t="n">
-        <v>12</v>
-      </c>
-      <c r="L13" s="30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5520,4 +5618,544 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MSFT — LOUGHRAN-MCDONALD FINANCIAL SENTIMENT ANALYSIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Item 7 (MD&amp;A) Natural Language Processing — Loughran-McDonald Lexicon (2011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Fiscal Year</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Raw MD&amp;A Words</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Cleaned MD&amp;A Words</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Positive Count</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Negative Count</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Net Score</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>P/N Ratio</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>Net Sentiment %</t>
+        </is>
+      </c>
+      <c r="I3" s="20" t="inlineStr">
+        <is>
+          <t>Uncertainty Count</t>
+        </is>
+      </c>
+      <c r="J3" s="20" t="inlineStr">
+        <is>
+          <t>Litigious Count</t>
+        </is>
+      </c>
+      <c r="K3" s="20" t="inlineStr">
+        <is>
+          <t>Strong Modal</t>
+        </is>
+      </c>
+      <c r="L3" s="20" t="inlineStr">
+        <is>
+          <t>Weak Modal</t>
+        </is>
+      </c>
+      <c r="M3" s="20" t="inlineStr">
+        <is>
+          <t>Tone Classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="21" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="22" t="n">
+        <v>11480</v>
+      </c>
+      <c r="C4" s="22" t="n">
+        <v>6850</v>
+      </c>
+      <c r="D4" s="22" t="n">
+        <v>162</v>
+      </c>
+      <c r="E4" s="22" t="n">
+        <v>310</v>
+      </c>
+      <c r="F4" s="22" t="n">
+        <v>-148</v>
+      </c>
+      <c r="G4" s="23" t="n">
+        <v>0.5226</v>
+      </c>
+      <c r="H4" s="24" t="n">
+        <v>-0.0216</v>
+      </c>
+      <c r="I4" s="22" t="n">
+        <v>105</v>
+      </c>
+      <c r="J4" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="K4" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="26" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B5" s="27" t="n">
+        <v>10679</v>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>6426</v>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>152</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>289</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>-137</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>-0.0213</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>97</v>
+      </c>
+      <c r="J5" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="K5" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="L5" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" s="25" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="21" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B6" s="22" t="n">
+        <v>10054</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>5965</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>156</v>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>210</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>-54</v>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>0.7429</v>
+      </c>
+      <c r="H6" s="24" t="n">
+        <v>-0.0091</v>
+      </c>
+      <c r="I6" s="22" t="n">
+        <v>79</v>
+      </c>
+      <c r="J6" s="22" t="n">
+        <v>39</v>
+      </c>
+      <c r="K6" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" s="25" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="26" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>9607</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>5674</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>170</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>159</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>1.0692</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="I7" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="J7" s="27" t="n">
+        <v>38</v>
+      </c>
+      <c r="K7" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" s="30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="21" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B8" s="22" t="n">
+        <v>9944</v>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>5962</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>185</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>148</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H8" s="24" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="I8" s="22" t="n">
+        <v>97</v>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="L8" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="M8" s="30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="26" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B9" s="27" t="n">
+        <v>8438</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>5076</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>157</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>124</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>33</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>1.2661</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>72</v>
+      </c>
+      <c r="J9" s="27" t="n">
+        <v>42</v>
+      </c>
+      <c r="K9" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="M9" s="30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="21" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B10" s="22" t="n">
+        <v>8335</v>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>5008</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>161</v>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>104</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>57</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>1.5481</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="I10" s="22" t="n">
+        <v>79</v>
+      </c>
+      <c r="J10" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="L10" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" s="30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="26" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B11" s="27" t="n">
+        <v>8412</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>5073</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>148</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>159</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>0.9308</v>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>77</v>
+      </c>
+      <c r="J11" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="K11" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="L11" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="M11" s="25" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>7738</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>4667</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>134</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>126</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>1.0635</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="I12" s="22" t="n">
+        <v>70</v>
+      </c>
+      <c r="J12" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="K12" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="L12" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" s="30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="27" t="n">
+        <v>7237</v>
+      </c>
+      <c r="C13" s="27" t="n">
+        <v>4300</v>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>133</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>116</v>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>1.1466</v>
+      </c>
+      <c r="H13" s="29" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I13" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="J13" s="27" t="n">
+        <v>31</v>
+      </c>
+      <c r="K13" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="L13" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="M13" s="30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>